--- a/outputs/list_of_plotted.xlsx
+++ b/outputs/list_of_plotted.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="408">
   <si>
     <t xml:space="preserve">variable_time</t>
   </si>
@@ -720,6 +720,9 @@
   </si>
   <si>
     <t xml:space="preserve">Pct_Neutrophil__week12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pct_CD162_IL10_Neutrophil__week21</t>
   </si>
   <si>
     <t xml:space="preserve">Pct_IL10_Neutrophil__week21</t>
@@ -5728,6 +5731,9 @@
         <v>229</v>
       </c>
       <c r="L1" t="s">
+        <v>230</v>
+      </c>
+      <c r="M1" t="s">
         <v>176</v>
       </c>
     </row>
@@ -5763,9 +5769,12 @@
         <v>0.342</v>
       </c>
       <c r="K2" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="L2" t="n">
         <v>13.49</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5801,9 +5810,12 @@
         <v>0.1576</v>
       </c>
       <c r="K3" t="n">
+        <v>5.742</v>
+      </c>
+      <c r="L3" t="n">
         <v>7.168</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5839,9 +5851,12 @@
         <v>0.304</v>
       </c>
       <c r="K4" t="n">
+        <v>5.846</v>
+      </c>
+      <c r="L4" t="n">
         <v>6.889</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5877,9 +5892,12 @@
         <v>0.6032</v>
       </c>
       <c r="K5" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="L5" t="n">
         <v>1.544</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5915,9 +5933,12 @@
         <v>0.2099</v>
       </c>
       <c r="K6" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="L6" t="s">
+        <v>12.04</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="M6" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5955,7 +5976,10 @@
       <c r="K7" t="n">
         <v>39.24</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="M7" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5991,9 +6015,12 @@
         <v>0.7975</v>
       </c>
       <c r="K8" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="L8" t="n">
         <v>37.25</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>178</v>
       </c>
     </row>
@@ -6031,7 +6058,10 @@
       <c r="K9" t="n">
         <v>7.12</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="M9" t="s">
         <v>178</v>
       </c>
     </row>
@@ -6067,9 +6097,12 @@
         <v>0.2248</v>
       </c>
       <c r="K10" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="L10" t="n">
         <v>27.05</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>178</v>
       </c>
     </row>
@@ -6105,9 +6138,12 @@
         <v>0.7019</v>
       </c>
       <c r="K11" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="L11" t="n">
         <v>43.86</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>178</v>
       </c>
     </row>
@@ -6143,9 +6179,12 @@
         <v>2.466</v>
       </c>
       <c r="K12" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="L12" t="n">
         <v>35.28</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6181,9 +6220,12 @@
         <v>1.729</v>
       </c>
       <c r="K13" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="L13" t="n">
         <v>39.89</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6219,9 +6261,12 @@
         <v>0.2149</v>
       </c>
       <c r="K14" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="L14" t="n">
         <v>28.97</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6257,9 +6302,12 @@
         <v>1.246</v>
       </c>
       <c r="K15" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="L15" t="n">
         <v>32.68</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6295,9 +6343,12 @@
         <v>2.393</v>
       </c>
       <c r="K16" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="L16" t="n">
         <v>36.47</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6314,7 +6365,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -6330,7 +6381,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -6358,19 +6409,19 @@
         <v>133</v>
       </c>
       <c r="E1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J1" t="s">
         <v>176</v>
@@ -6849,34 +6900,34 @@
         <v>133</v>
       </c>
       <c r="E1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O1" t="s">
         <v>176</v>
@@ -7531,7 +7582,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -7559,67 +7610,67 @@
         <v>133</v>
       </c>
       <c r="E1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="U1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="V1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="X1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z1" t="s">
         <v>176</v>
@@ -9082,115 +9133,115 @@
         <v>133</v>
       </c>
       <c r="E1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K1" t="s">
+        <v>269</v>
+      </c>
+      <c r="L1" t="s">
+        <v>270</v>
+      </c>
+      <c r="M1" t="s">
+        <v>239</v>
+      </c>
+      <c r="N1" t="s">
+        <v>271</v>
+      </c>
+      <c r="O1" t="s">
+        <v>238</v>
+      </c>
+      <c r="P1" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>272</v>
+      </c>
+      <c r="R1" t="s">
+        <v>240</v>
+      </c>
+      <c r="S1" t="s">
+        <v>241</v>
+      </c>
+      <c r="T1" t="s">
+        <v>273</v>
+      </c>
+      <c r="U1" t="s">
+        <v>274</v>
+      </c>
+      <c r="V1" t="s">
+        <v>235</v>
+      </c>
+      <c r="W1" t="s">
+        <v>275</v>
+      </c>
+      <c r="X1" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>278</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>280</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>281</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>282</v>
+      </c>
+      <c r="AG1" t="s">
         <v>263</v>
       </c>
-      <c r="F1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G1" t="s">
-        <v>264</v>
-      </c>
-      <c r="H1" t="s">
-        <v>265</v>
-      </c>
-      <c r="I1" t="s">
-        <v>266</v>
-      </c>
-      <c r="J1" t="s">
-        <v>267</v>
-      </c>
-      <c r="K1" t="s">
-        <v>268</v>
-      </c>
-      <c r="L1" t="s">
-        <v>269</v>
-      </c>
-      <c r="M1" t="s">
-        <v>238</v>
-      </c>
-      <c r="N1" t="s">
-        <v>270</v>
-      </c>
-      <c r="O1" t="s">
-        <v>237</v>
-      </c>
-      <c r="P1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>271</v>
-      </c>
-      <c r="R1" t="s">
-        <v>239</v>
-      </c>
-      <c r="S1" t="s">
-        <v>240</v>
-      </c>
-      <c r="T1" t="s">
-        <v>272</v>
-      </c>
-      <c r="U1" t="s">
-        <v>273</v>
-      </c>
-      <c r="V1" t="s">
-        <v>234</v>
-      </c>
-      <c r="W1" t="s">
-        <v>274</v>
-      </c>
-      <c r="X1" t="s">
-        <v>275</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>276</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>278</v>
-      </c>
-      <c r="AB1" t="s">
+      <c r="AH1" t="s">
+        <v>283</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>284</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>285</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>286</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>243</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>244</v>
+      </c>
+      <c r="AN1" t="s">
         <v>245</v>
       </c>
-      <c r="AC1" t="s">
-        <v>241</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>279</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>280</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>281</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>262</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>282</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>283</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>284</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>242</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>243</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>244</v>
-      </c>
       <c r="AO1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AP1" t="s">
         <v>176</v>
@@ -17650,7 +17701,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -17682,7 +17733,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -17714,7 +17765,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -17746,7 +17797,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -17778,7 +17829,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -17810,7 +17861,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -17842,7 +17893,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -17874,7 +17925,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -17906,7 +17957,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -17932,7 +17983,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -17958,7 +18009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -17990,7 +18041,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -18022,7 +18073,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -18054,7 +18105,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
@@ -18086,7 +18137,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -18118,7 +18169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -18150,7 +18201,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -18182,7 +18233,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
@@ -18208,7 +18259,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -18234,7 +18285,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -18266,7 +18317,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
@@ -18298,7 +18349,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
@@ -18330,7 +18381,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -18362,7 +18413,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
@@ -18394,7 +18445,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -18426,7 +18477,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
@@ -18458,7 +18509,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
@@ -18484,7 +18535,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -18510,7 +18561,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -18542,7 +18593,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -18574,7 +18625,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B31" t="n">
         <v>1</v>
@@ -18606,7 +18657,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -18638,7 +18689,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -18670,7 +18721,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -18702,7 +18753,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B35" t="n">
         <v>1</v>
@@ -18734,7 +18785,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -18760,7 +18811,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B37" t="n">
         <v>0</v>
@@ -18786,7 +18837,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B38" t="n">
         <v>0</v>
@@ -18818,7 +18869,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B39" t="n">
         <v>1</v>
@@ -18850,7 +18901,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B40" t="n">
         <v>0</v>
@@ -18882,7 +18933,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B41" t="n">
         <v>0</v>
@@ -18914,7 +18965,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
@@ -18946,7 +18997,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
@@ -18978,7 +19029,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
@@ -19010,7 +19061,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
@@ -19036,7 +19087,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
@@ -19062,7 +19113,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
@@ -19094,7 +19145,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
@@ -19126,7 +19177,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B49" t="n">
         <v>1</v>
@@ -19158,7 +19209,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
@@ -19190,7 +19241,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
@@ -19222,7 +19273,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
@@ -19254,7 +19305,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B53" t="n">
         <v>0</v>
@@ -19286,7 +19337,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B54" t="n">
         <v>1</v>
@@ -19312,7 +19363,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B55" t="n">
         <v>0</v>
@@ -19338,7 +19389,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B56" t="n">
         <v>0</v>
@@ -19370,7 +19421,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B57" t="n">
         <v>0</v>
@@ -19402,7 +19453,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B58" t="n">
         <v>1</v>
@@ -19434,7 +19485,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B59" t="n">
         <v>1</v>
@@ -19466,7 +19517,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B60" t="n">
         <v>0</v>
@@ -19498,7 +19549,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B61" t="n">
         <v>0</v>
@@ -19530,7 +19581,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -19562,7 +19613,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B63" t="n">
         <v>1</v>
@@ -19588,7 +19639,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B64" t="n">
         <v>0</v>
@@ -19614,7 +19665,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B65" t="n">
         <v>0</v>
@@ -19646,7 +19697,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B66" t="n">
         <v>2</v>
@@ -19678,7 +19729,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B67" t="n">
         <v>6</v>
@@ -19710,7 +19761,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B68" t="n">
         <v>3</v>
@@ -19742,7 +19793,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
@@ -19774,7 +19825,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B70" t="n">
         <v>1</v>
@@ -19806,7 +19857,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B71" t="n">
         <v>3</v>
@@ -19838,7 +19889,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B72" t="n">
         <v>6</v>
@@ -19864,7 +19915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B73" t="n">
         <v>0</v>
@@ -19890,7 +19941,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B74" t="n">
         <v>3</v>
@@ -19916,7 +19967,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B75" t="n">
         <v>5</v>
@@ -19942,7 +19993,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B76" t="n">
         <v>3</v>
@@ -19968,7 +20019,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B77" t="n">
         <v>3</v>
@@ -19994,7 +20045,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B78" t="n">
         <v>2</v>
@@ -20020,7 +20071,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B79" t="n">
         <v>2</v>
@@ -20046,7 +20097,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B80" t="n">
         <v>3</v>
@@ -20083,7 +20134,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -20112,7 +20163,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -20141,7 +20192,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -20170,7 +20221,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -20199,7 +20250,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -20228,7 +20279,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -20257,7 +20308,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -20286,7 +20337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -20315,7 +20366,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -20338,7 +20389,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -20361,7 +20412,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -20390,7 +20441,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -20419,7 +20470,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -20448,7 +20499,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
@@ -20477,7 +20528,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -20506,7 +20557,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -20535,7 +20586,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -20564,7 +20615,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
@@ -20587,7 +20638,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -20610,7 +20661,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -20639,7 +20690,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
@@ -20668,7 +20719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
@@ -20697,7 +20748,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -20726,7 +20777,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
@@ -20755,7 +20806,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -20784,7 +20835,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
@@ -20813,7 +20864,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
@@ -20836,7 +20887,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -20859,7 +20910,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -20888,7 +20939,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -20917,7 +20968,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B31" t="n">
         <v>1</v>
@@ -20946,7 +20997,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -20975,7 +21026,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -21004,7 +21055,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -21033,7 +21084,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B35" t="n">
         <v>1</v>
@@ -21062,7 +21113,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -21085,7 +21136,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B37" t="n">
         <v>0</v>
@@ -21108,7 +21159,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B38" t="n">
         <v>0</v>
@@ -21137,7 +21188,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B39" t="n">
         <v>1</v>
@@ -21166,7 +21217,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B40" t="n">
         <v>0</v>
@@ -21195,7 +21246,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B41" t="n">
         <v>0</v>
@@ -21224,7 +21275,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
@@ -21253,7 +21304,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
@@ -21282,7 +21333,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
@@ -21311,7 +21362,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
@@ -21334,7 +21385,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
@@ -21357,7 +21408,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
@@ -21386,7 +21437,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
@@ -21415,7 +21466,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B49" t="n">
         <v>1</v>
@@ -21444,7 +21495,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
@@ -21473,7 +21524,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
@@ -21502,7 +21553,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
@@ -21531,7 +21582,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B53" t="n">
         <v>0</v>
@@ -21560,7 +21611,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B54" t="n">
         <v>1</v>
@@ -21583,7 +21634,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B55" t="n">
         <v>0</v>
@@ -21606,7 +21657,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B56" t="n">
         <v>0</v>
@@ -21635,7 +21686,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B57" t="n">
         <v>0</v>
@@ -21664,7 +21715,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B58" t="n">
         <v>1</v>
@@ -21693,7 +21744,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B59" t="n">
         <v>1</v>
@@ -21722,7 +21773,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B60" t="n">
         <v>0</v>
@@ -21751,7 +21802,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B61" t="n">
         <v>0</v>
@@ -21780,7 +21831,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -21809,7 +21860,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B63" t="n">
         <v>1</v>
@@ -21832,7 +21883,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B64" t="n">
         <v>0</v>
@@ -21855,7 +21906,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B65" t="n">
         <v>0</v>
@@ -21884,7 +21935,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B66" t="n">
         <v>2</v>
@@ -21913,7 +21964,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B67" t="n">
         <v>6</v>
@@ -21942,7 +21993,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B68" t="n">
         <v>3</v>
@@ -21971,7 +22022,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
@@ -22000,7 +22051,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B70" t="n">
         <v>1</v>
@@ -22029,7 +22080,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B71" t="n">
         <v>3</v>
@@ -22058,7 +22109,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B72" t="n">
         <v>6</v>
@@ -22081,7 +22132,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B73" t="n">
         <v>0</v>
@@ -22104,7 +22155,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B74" t="n">
         <v>3</v>
@@ -22127,7 +22178,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B75" t="n">
         <v>5</v>
@@ -22150,7 +22201,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B76" t="n">
         <v>3</v>
@@ -22173,7 +22224,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B77" t="n">
         <v>3</v>
@@ -22196,7 +22247,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B78" t="n">
         <v>2</v>
@@ -22219,7 +22270,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B79" t="n">
         <v>2</v>
@@ -22242,7 +22293,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B80" t="n">
         <v>3</v>
@@ -22276,75 +22327,75 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="S1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B2" t="n">
         <v>0.4379</v>
@@ -22407,12 +22458,12 @@
         <v>551.1</v>
       </c>
       <c r="V2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B3" t="n">
         <v>0.3834</v>
@@ -22471,12 +22522,12 @@
         <v>406.9</v>
       </c>
       <c r="V3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B4" t="n">
         <v>0.0749</v>
@@ -22539,12 +22590,12 @@
         <v>492.9</v>
       </c>
       <c r="V4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B5" t="n">
         <v>0.5878</v>
@@ -22605,12 +22656,12 @@
         <v>595</v>
       </c>
       <c r="V5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B6" t="n">
         <v>0.7578</v>
@@ -22673,12 +22724,12 @@
         <v>763.6</v>
       </c>
       <c r="V6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B7" t="n">
         <v>0.1397</v>
@@ -22739,12 +22790,12 @@
         <v>498.9</v>
       </c>
       <c r="V7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B8" t="n">
         <v>0.1119</v>
@@ -22807,12 +22858,12 @@
         <v>623</v>
       </c>
       <c r="V8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B9" t="n">
         <v>0.04361</v>
@@ -22873,12 +22924,12 @@
         <v>546.8</v>
       </c>
       <c r="V9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B10" t="n">
         <v>0.04299</v>
@@ -22939,12 +22990,12 @@
         <v>0.02948</v>
       </c>
       <c r="V10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B11" t="n">
         <v>3.011</v>
@@ -23007,12 +23058,12 @@
         <v>2.748</v>
       </c>
       <c r="V11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B12" t="n">
         <v>4.215</v>
@@ -23075,12 +23126,12 @@
         <v>2.721</v>
       </c>
       <c r="V12" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B13" t="n">
         <v>2.788</v>
@@ -23143,12 +23194,12 @@
         <v>2.672</v>
       </c>
       <c r="V13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B14" t="n">
         <v>1.416</v>
@@ -23211,12 +23262,12 @@
         <v>2.592</v>
       </c>
       <c r="V14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B15" t="n">
         <v>4.959</v>
@@ -23279,12 +23330,12 @@
         <v>3.439</v>
       </c>
       <c r="V15" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B16" t="n">
         <v>0.5662</v>
@@ -23347,12 +23398,12 @@
         <v>19.28</v>
       </c>
       <c r="V16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B17" t="n">
         <v>0.8516</v>
@@ -23415,7 +23466,7 @@
         <v>21.76</v>
       </c>
       <c r="V17" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
